--- a/멀티 입력 예시.xlsx
+++ b/멀티 입력 예시.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\OneDrive Backup\Minwon-Factory\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\OneDrive Backup\Minwon-Factory\Minwon_Factory(Streamlit 1.49)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E46C7B-7E5B-4546-BC2C-57768BFEFEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07411926-41ED-4637-B7DF-54FA16626326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9FD4BDAD-AC66-4962-B5C5-7ACA93211E64}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{9FD4BDAD-AC66-4962-B5C5-7ACA93211E64}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
   <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,19 +71,6 @@
   </si>
   <si>
     <t>테스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다대포해상풍력단지 조성에 있어 주민들은 지속적으로 반대의 의견을 내비춰왔습니다.
-그럼에도 불구하고 구청장께서 기사를 내실 정도로 왜 자꾸 추진하시려는지 이해가 되지 않습니다.
-다대포 인근에 지역주민이 매우 많이 살고 있습니다.
-어촌은 아주 극히 소수이고요. 아파트에 거주하고 있는 지역주민이 대다수입니다.
-다대포는 주민이 살지 않는 시골마을이 아닌 주민이 많이 살고 있는 도시지역입니다.
-이런 주민들을 뒤로 하고 풍력단지를 조성하여 얻는 이익이 무엇입니까?
-좀 알고 싶습니다.
-사하구에는 감천에 화력발전소도 있습니다.
-지역주민이 반대하는 시설을 구청이 왜 앞장서서 추진하시는지 이해가 되질 않습니다.
-저만 이해가 안 가는걸까요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -541,7 +528,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="409.5">
+    <row r="2" spans="1:4" ht="82.5">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -555,46 +542,41 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="313.5">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" ht="132">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="409.5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
